--- a/pacjenci/ELŻBIETA GALAS.xlsx
+++ b/pacjenci/ELŻBIETA GALAS.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>06.12.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak DLBCL. Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 104mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Aktywne metabolicznie węzły chłonne: - przedziałów IB- V oraz nadobojczykowe pojedyncze i spakietowane, z naciekiem lewego płata tarczycy - o łącznym wymiarze wielkości do 71x32mm wg PET, SUV max do 7,8; - przedziału III po stronie prawej wielkości do 17mm wg PET, SUV max do 14,2. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik korowo-podkorowy mózgu i móżdżku. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - przytchawiczy górny lewy wielkości 11mm wg PET, SUV max 7,0; - pachowy lewy wielkości 9mm, SUV max 3,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nawarstwienia opłucnowe ze zwapnieniami w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywne metabolicznie obszary w śledzionie: - w górnym biegunie, wielkości 19mm, SUV max 13,6, uwypuklający się poza obrys śledziony dobrzusznie i ku górze; - w dolnym biegunie, wielkości 16mm wg PET, SUV max 9,3. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Macica powiększona, o nieregularnych obrysach.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, [piersiowym i lędźwiowym kręgosłupa. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tt. potomnych.  Wartości referencyjne: MBPS SUVmax do 2,9; Prawy płat wątroby SUVmax do 4,2.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych powyżej poziomu przepony oraz aktywnych metabolicznie zmian w śledzionie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>14.2</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>16.02.2023</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak DLBCL. Stan po zakończonym leczeniu 06.2022 oraz po konsolidacyjnej radioterapii. Ocena remisji choroby 3 m-ce po zakończeniu IFRT.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 81 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Niejednorodne, mierne pobudzenie metaboliczne w tarczycy, SUV max do 3,8 - większe po stronie prawej - do kontroli w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik korowo-podkorowy mózgu i móżdżku. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - przytchawicze dolne prawe, wielkości do 9 mm SUV max do 5,1; - wnęki płuca prawego, wielkości do 11 mm wg PET SUV max do 8,9. Pobudzone metabolicznie węzły chłonne okna aortalno-płucnego i wnęki płuca lewego, średnicy do 8 mm SUV max 3,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nawarstwienia opłucnowe ze zwapnieniami w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Drobne zwapnienia w topografii obu kopuł przepony. Port naczyniowy zaimplantowany podobojczykowo po stronie prawej.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Macica powiększona, o nieregularnych obrysach. Węzły chłonne pachwinowe obustronnie wielkości do 9mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Cechy uogólnionego zaniku kostnego. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa [ciasne na poziomie L4/L5 i L5/S1 z cechami vacuum phenomen krążka międzykręgowego]. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tt. potomnych.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 4,1.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych i pobudzonych metabolicznie węzłów chłonnych w klatce piersiowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>8.9</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>17.07.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak DLBCL. Stan po zakończonym leczeniu 06.2022 oraz po konsolidacyjnej radioterapii. Ocena remisji choroby w kontekście zmian w obrębie płuc.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 86 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Niejednorodne, mierne pobudzenie metaboliczne w tarczycy - większe po stronie prawej - opisywane już poprzednio. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik korowo-podkorowy mózgu i móżdżku. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - okna aortalno-płucnego i wnęki płuca lewego, średnicy do 8 mm SUV max do 4,2 - przytchawicze dolne prawe, wielkości do 10 mm wg PET, SUV max do 5,3 - wnęki płuca prawego, wielkości do 16 mm wg PET, SUV max do 8,0. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nawarstwienia opłucnowe ze zwapnieniami w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Drobne zwapnienia w topografii obu kopuł przepony.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Macica powiększona, o nieregularnych obrysach. Węzły chłonne pachwinowe obustronnie wielkości do 9mm.  Układ kostny: Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z odcinkowym pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Cechy uogólnionego zaniku kostnego. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa [ciasne na poziomie L4/L5 i L5/S1 z cechami vacuum phenomen krążka międzykręgowego]. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tt. potomnych.    Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 4,1.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych i pobudzonych metabolicznie węzłów chłonnych w klatce piersiowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>8</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/ELŻBIETA GALAS.xlsx
+++ b/pacjenci/ELŻBIETA GALAS.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 104mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne: - przedziałów IB- V oraz nadobojczykowe pojedyncze i spakietowane, z naciekiem lewego płata tarczycy - o łącznym wymiarze wielkości do 71x32mm wg PET, SUV max do 7,8; - przedziału III po stronie prawej wielkości do 17mm wg PET, SUV max do 14,2. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik korowo-podkorowy mózgu i móżdżku. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - przytchawiczy górny lewy wielkości 11mm wg PET, SUV max 7,0; - pachowy lewy wielkości 9mm, SUV max 3,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nawarstwienia opłucnowe ze zwapnieniami w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywne metabolicznie obszary w śledzionie: - w górnym biegunie, wielkości 19mm, SUV max 13,6, uwypuklający się poza obrys śledziony dobrzusznie i ku górze; - w dolnym biegunie, wielkości 16mm wg PET, SUV max 9,3. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Macica powiększona, o nieregularnych obrysach.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, [piersiowym i lędźwiowym kręgosłupa. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tt. potomnych.  Wartości referencyjne: MBPS SUVmax do 2,9; Prawy płat wątroby SUVmax do 4,2.</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - przedziałów IB- V oraz nadobojczykowe pojedyncze i spakietowane, z naciekiem lewego płata tarczycy - o łącznym wymiarze wielkości do 71x32mm wg PET, SUV max do 7,8; - przedziału III po stronie prawej wielkości do 17mm wg PET, SUV max do 14,2. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik korowo-podkorowy mózgu i móżdżku. Hypoplazja zatok czołowych. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - przytchawiczy górny lewy wielkości 11mm wg PET, SUV max 7,0; - pachowy lewy wielkości 9mm, SUV max 3,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nawarstwienia opłucnowe ze zwapnieniami w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie obszary w śledzionie: - w górnym biegunie, wielkości 19mm, SUV max 13,6, uwypuklający się poza obrys śledziony dobrzusznie i ku górze; - w dolnym biegunie, wielkości 16mm wg PET, SUV max 9,3. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Macica powiększona, o nieregularnych obrysach.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, [piersiowym i lędźwiowym kręgosłupa. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tt. potomnych.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych powyżej poziomu przepony oraz aktywnych metabolicznie zmian w śledzionie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>14.2</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 81 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Niejednorodne, mierne pobudzenie metaboliczne w tarczycy, SUV max do 3,8 - większe po stronie prawej - do kontroli w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik korowo-podkorowy mózgu i móżdżku. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - przytchawicze dolne prawe, wielkości do 9 mm SUV max do 5,1; - wnęki płuca prawego, wielkości do 11 mm wg PET SUV max do 8,9. Pobudzone metabolicznie węzły chłonne okna aortalno-płucnego i wnęki płuca lewego, średnicy do 8 mm SUV max 3,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nawarstwienia opłucnowe ze zwapnieniami w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Drobne zwapnienia w topografii obu kopuł przepony. Port naczyniowy zaimplantowany podobojczykowo po stronie prawej.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Macica powiększona, o nieregularnych obrysach. Węzły chłonne pachwinowe obustronnie wielkości do 9mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Cechy uogólnionego zaniku kostnego. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa [ciasne na poziomie L4/L5 i L5/S1 z cechami vacuum phenomen krążka międzykręgowego]. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tt. potomnych.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 4,1.</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Niejednorodne, mierne pobudzenie metaboliczne w tarczycy, SUV max do 3,8 - większe po stronie prawej - do kontroli w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik korowo-podkorowy mózgu i móżdżku. Hypoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - przytchawicze dolne prawe, wielkości do 9 mm SUV max do 5,1; - wnęki płuca prawego, wielkości do 11 mm wg PET SUV max do 8,9. Pobudzone metabolicznie węzły chłonne okna aortalno-płucnego i wnęki płuca lewego, średnicy do 8 mm SUV max 3,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nawarstwienia opłucnowe ze zwapnieniami w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Drobne zwapnienia w topografii obu kopuł przepony. Port naczyniowy zaimplantowany podobojczykowo po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Macica powiększona, o nieregularnych obrysach. Węzły chłonne pachwinowe obustronnie wielkości do 9mm.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Cechy uogólnionego zaniku kostnego. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa [ciasne na poziomie L4/L5 i L5/S1 z cechami vacuum phenomen krążka międzykręgowego]. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tt. potomnych.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych i pobudzonych metabolicznie węzłów chłonnych w klatce piersiowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>8.9</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 86 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Niejednorodne, mierne pobudzenie metaboliczne w tarczycy - większe po stronie prawej - opisywane już poprzednio. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik korowo-podkorowy mózgu i móżdżku. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - okna aortalno-płucnego i wnęki płuca lewego, średnicy do 8 mm SUV max do 4,2 - przytchawicze dolne prawe, wielkości do 10 mm wg PET, SUV max do 5,3 - wnęki płuca prawego, wielkości do 16 mm wg PET, SUV max do 8,0. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nawarstwienia opłucnowe ze zwapnieniami w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Drobne zwapnienia w topografii obu kopuł przepony.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Macica powiększona, o nieregularnych obrysach. Węzły chłonne pachwinowe obustronnie wielkości do 9mm.  Układ kostny: Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z odcinkowym pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Cechy uogólnionego zaniku kostnego. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa [ciasne na poziomie L4/L5 i L5/S1 z cechami vacuum phenomen krążka międzykręgowego]. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tt. potomnych.    Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 4,1.</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Niejednorodne, mierne pobudzenie metaboliczne w tarczycy - większe po stronie prawej - opisywane już poprzednio. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik korowo-podkorowy mózgu i móżdżku. Hypoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - okna aortalno-płucnego i wnęki płuca lewego, średnicy do 8 mm SUV max do 4,2 - przytchawicze dolne prawe, wielkości do 10 mm wg PET, SUV max do 5,3 - wnęki płuca prawego, wielkości do 16 mm wg PET, SUV max do 8,0. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nawarstwienia opłucnowe ze zwapnieniami w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Drobne zwapnienia w topografii obu kopuł przepony.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Macica powiększona, o nieregularnych obrysach. Węzły chłonne pachwinowe obustronnie wielkości do 9mm.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z odcinkowym pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Cechy uogólnionego zaniku kostnego. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa [ciasne na poziomie L4/L5 i L5/S1 z cechami vacuum phenomen krążka międzykręgowego]. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tt. potomnych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych i pobudzonych metabolicznie węzłów chłonnych w klatce piersiowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>8</v>
       </c>
     </row>
